--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486745_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486745_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1734</v>
+        <v>6.0449</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3309</v>
+        <v>6.848</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1575</v>
+        <v>-0.8031</v>
       </c>
       <c r="G2" t="n">
         <v>3.5247</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>0.37</v>
+        <v>0.2415</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1038</v>
+        <v>-0.5867</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4738</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.7341</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1281</v>
+        <v>5.7022</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8948</v>
+        <v>6.1709</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7667</v>
+        <v>-0.4687</v>
       </c>
       <c r="G3" t="n">
         <v>1.218</v>
@@ -688,13 +688,13 @@
         <v>2.1239</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8052</v>
+        <v>0.3792</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0477</v>
+        <v>0.3238</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2426</v>
+        <v>0.0554</v>
       </c>
       <c r="V3" t="n">
         <v>2.9465</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.555</v>
+        <v>5.4101</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4873</v>
+        <v>3.5908</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0677</v>
+        <v>1.8193</v>
       </c>
       <c r="G4" t="n">
         <v>2.0974</v>
@@ -766,13 +766,13 @@
         <v>2.3169</v>
       </c>
       <c r="S4" t="n">
-        <v>0.607</v>
+        <v>0.4621</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.028</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.635</v>
+        <v>0.3867</v>
       </c>
       <c r="V4" t="n">
         <v>0.5337</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.752</v>
+        <v>0.8265</v>
       </c>
       <c r="E5" t="n">
         <v>-0.0074</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7593</v>
+        <v>0.8338</v>
       </c>
       <c r="G5" t="n">
         <v>0.1507</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>0.022</v>
+        <v>0.0965</v>
       </c>
       <c r="T5" t="n">
         <v>0.1377</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1156</v>
+        <v>-0.0411</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. SANCHEZ PARRA</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8689</v>
+        <v>-0.9982</v>
       </c>
       <c r="E6" t="n">
-        <v>0.17</v>
+        <v>-0.2589</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0388</v>
+        <v>-0.7393</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.3058</v>
+        <v>-2.5275</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8197</v>
+        <v>-2.1589</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4861</v>
+        <v>-0.3685</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1716</v>
+        <v>-0.0848</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0088</v>
+        <v>-0.7789</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1628</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.4774</v>
+        <v>-2.4426</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.8285</v>
+        <v>-1.3801</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6489</v>
+        <v>-1.0626</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1931</v>
+        <v>1.7377</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7031</v>
+        <v>1.7377</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4671</v>
+        <v>-0.4139</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3233</v>
+        <v>-0.7453</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1438</v>
+        <v>0.3314</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1628</v>
+        <v>0.2055</v>
       </c>
       <c r="W6" t="n">
         <v>0.5712</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4084</v>
+        <v>-0.3658</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3622</v>
+        <v>-1.2092</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6726</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6896</v>
+        <v>-0.6079</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5275</v>
+        <v>-1.7952</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1589</v>
+        <v>-3.1787</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3685</v>
+        <v>1.3835</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0848</v>
+        <v>-0.1802</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7789</v>
+        <v>-2.6263</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6941000000000001</v>
+        <v>2.4461</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4426</v>
+        <v>-1.6149</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3801</v>
+        <v>-0.5524</v>
       </c>
       <c r="O7" t="n">
         <v>-1.0626</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7779</v>
+        <v>-0.3794</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1589</v>
+        <v>-0.4211</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3811</v>
+        <v>0.0417</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2055</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4107</v>
+        <v>-1.3113</v>
       </c>
       <c r="E8" t="n">
         <v>1.0546</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4653</v>
+        <v>-2.3659</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0631</v>
@@ -1078,13 +1078,13 @@
         <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5407</v>
+        <v>-0.4413</v>
       </c>
       <c r="T8" t="n">
         <v>-0.3311</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2096</v>
+        <v>-0.1102</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>S. SANCHEZ PARRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9995</v>
+        <v>-1.8534</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1185</v>
+        <v>-0.8643</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.881</v>
+        <v>-0.9892</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7952</v>
+        <v>-2.3058</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.1787</v>
+        <v>-1.8197</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3835</v>
+        <v>-0.4861</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1802</v>
+        <v>1.1716</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.6263</v>
+        <v>1.0088</v>
       </c>
       <c r="L9" t="n">
-        <v>2.4461</v>
+        <v>0.1628</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6149</v>
+        <v>-3.4774</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5524</v>
+        <v>-2.8285</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0626</v>
+        <v>-0.6489</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9654</v>
+        <v>2.7031</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1697</v>
+        <v>0.4826</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9382</v>
+        <v>0.2891</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2315</v>
+        <v>0.1935</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1628</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.4084</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2138</v>
+        <v>-1.9821</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.4066</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6004</v>
+        <v>-1.5755</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9998</v>
@@ -1234,13 +1234,13 @@
         <v>0.5792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.2759</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2484</v>
+        <v>-0.0415</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2592</v>
+        <v>-0.2344</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2856</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.871</v>
+        <v>-2.7468</v>
       </c>
       <c r="E11" t="n">
         <v>0.1642</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0352</v>
+        <v>-2.9111</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6777</v>
@@ -1312,13 +1312,13 @@
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9656</v>
+        <v>-0.8414</v>
       </c>
       <c r="T11" t="n">
         <v>-0.6347</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3309</v>
+        <v>-0.2068</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.882399999999999</v>
+        <v>7.8827</v>
       </c>
       <c r="E12" t="n">
-        <v>15.6899</v>
+        <v>15.69</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.807499999999999</v>
+        <v>-7.807599999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-5.378299999999999</v>
@@ -1390,7 +1390,7 @@
         <v>15.4462</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6901999999999999</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>-1.9344</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0527</v>
+        <v>5.2291</v>
       </c>
       <c r="E13" t="n">
         <v>6.6097</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.557</v>
+        <v>-1.3806</v>
       </c>
       <c r="G13" t="n">
         <v>3.7397</v>
@@ -1468,13 +1468,13 @@
         <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1545</v>
+        <v>0.331</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4693</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6239</v>
+        <v>0.8003</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0466</v>
+        <v>3.7916</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6061</v>
+        <v>4.089</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5595</v>
+        <v>-0.2974</v>
       </c>
       <c r="G14" t="n">
         <v>3.3749</v>
@@ -1546,13 +1546,13 @@
         <v>0.5792</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7723</v>
+        <v>0.5172</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0549</v>
+        <v>0.2072</v>
       </c>
       <c r="V14" t="n">
         <v>0.2856</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5052</v>
+        <v>1.8321</v>
       </c>
       <c r="E15" t="n">
-        <v>2.594</v>
+        <v>2.6974</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0888</v>
+        <v>-0.8653</v>
       </c>
       <c r="G15" t="n">
         <v>1.9452</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1545</v>
+        <v>0.1725</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1655</v>
+        <v>-0.0621</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0111</v>
+        <v>0.2346</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2856</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8683</v>
+        <v>0.5043</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0635</v>
+        <v>1.6498</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1951</v>
+        <v>-1.1455</v>
       </c>
       <c r="G16" t="n">
         <v>1.2354</v>
@@ -1702,13 +1702,13 @@
         <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6675</v>
+        <v>0.3035</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3584</v>
+        <v>-0.0553</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3091</v>
+        <v>0.3588</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2277</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4478</v>
+        <v>-0.2354</v>
       </c>
       <c r="E17" t="n">
         <v>1.5301</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9779</v>
+        <v>-1.7655</v>
       </c>
       <c r="G17" t="n">
         <v>2.3603</v>
@@ -1780,13 +1780,13 @@
         <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4083</v>
+        <v>0.6207</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1934</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6017</v>
+        <v>0.8141</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8995</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5742</v>
+        <v>-0.3507</v>
       </c>
       <c r="E18" t="n">
         <v>0.2017</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7759</v>
+        <v>-0.5524</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0362</v>
@@ -1858,13 +1858,13 @@
         <v>0.5792</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4028</v>
+        <v>-0.1793</v>
       </c>
       <c r="T18" t="n">
         <v>0.1377</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5405</v>
+        <v>-0.317</v>
       </c>
       <c r="V18" t="n">
         <v>0.2856</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3357</v>
+        <v>-2.4504</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9372</v>
+        <v>-1.3166</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3985</v>
+        <v>-1.1338</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8244</v>
@@ -1936,13 +1936,13 @@
         <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8162</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9933</v>
+        <v>-0.3727</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1771</v>
+        <v>0.4418</v>
       </c>
       <c r="V19" t="n">
         <v>0.6565</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>M. OLIVA I CAMPABADAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.6702</v>
+        <v>-3.9459</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9268</v>
+        <v>-4.3668</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.7433</v>
+        <v>0.4209</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6587</v>
+        <v>-1.258</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.187</v>
+        <v>-0.0351</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4717</v>
+        <v>-1.223</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6782</v>
+        <v>-0.305</v>
       </c>
       <c r="K20" t="n">
-        <v>0.538</v>
+        <v>1.0694</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2162</v>
+        <v>-1.3744</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9805</v>
+        <v>-0.953</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.725</v>
+        <v>-1.1044</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2555</v>
+        <v>0.1514</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5792</v>
+        <v>-3.2823</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R20" t="n">
         <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4635</v>
+        <v>-0.0621</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2486</v>
+        <v>-0.2003</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2149</v>
+        <v>0.1382</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1271</v>
+        <v>0.6565</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1271</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. OLIVA I CAMPABADAL</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1251</v>
+        <v>-4.1998</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.884</v>
+        <v>-1.0302</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2411</v>
+        <v>-3.1696</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.258</v>
+        <v>-2.6587</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0351</v>
+        <v>-1.187</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.223</v>
+        <v>-1.4717</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.305</v>
+        <v>-0.6782</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0694</v>
+        <v>0.538</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3744</v>
+        <v>-1.2162</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.953</v>
+        <v>-1.9805</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1044</v>
+        <v>-1.725</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1514</v>
+        <v>-0.2555</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.2823</v>
+        <v>0.5792</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2412</v>
+        <v>0.0068</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7174</v>
+        <v>-0.352</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5238</v>
+        <v>0.3589</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6565</v>
+        <v>-2.1271</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6565</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2025</v>
+        <v>-5.9889</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0496</v>
+        <v>-2.2564</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1529</v>
+        <v>-3.7325</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5001</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7657</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2201</v>
+        <v>0.0133</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5456</v>
+        <v>0.966</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6412</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.882700000000001</v>
+        <v>-5.814000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>7.807500000000001</v>
+        <v>7.8077</v>
       </c>
       <c r="F23" t="n">
-        <v>-15.69</v>
+        <v>-13.6217</v>
       </c>
       <c r="G23" t="n">
-        <v>5.378099999999999</v>
+        <v>5.3781</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.002299999999999525</v>
+        <v>-0.002300000000000191</v>
       </c>
       <c r="I23" t="n">
-        <v>5.380500000000001</v>
+        <v>5.3805</v>
       </c>
       <c r="J23" t="n">
         <v>20.6997</v>
@@ -2227,7 +2227,7 @@
         <v>12.075</v>
       </c>
       <c r="L23" t="n">
-        <v>8.624899999999998</v>
+        <v>8.6249</v>
       </c>
       <c r="M23" t="n">
         <v>-15.3216</v>
@@ -2248,22 +2248,22 @@
         <v>5.7922</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6900999999999999</v>
+        <v>2.7586</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2442</v>
+        <v>-1.2441</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9344</v>
+        <v>4.0029</v>
       </c>
       <c r="V23" t="n">
-        <v>-4.296900000000001</v>
+        <v>-4.2969</v>
       </c>
       <c r="W23" t="n">
         <v>3.7983</v>
       </c>
       <c r="X23" t="n">
-        <v>-8.094999999999999</v>
+        <v>-8.095000000000001</v>
       </c>
     </row>
   </sheetData>
